--- a/admin_testy/reporty_google_testy/google_data/Pobočky/Předloha/Databaze Zličín 2024.xlsx
+++ b/admin_testy/reporty_google_testy/google_data/Pobočky/Předloha/Databaze Zličín 2024.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2163" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2184" uniqueCount="66">
   <si>
     <t>Datum</t>
   </si>
@@ -48074,6 +48074,566 @@
         <v>0.09523809523809523</v>
       </c>
     </row>
+    <row r="643">
+      <c r="A643" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B643" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P643" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S643" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T643" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U643" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V643" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W643" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X643" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB643" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC643" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD643" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI643" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ643" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK643" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL643" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM643" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN643" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO643" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP643" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ643" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR643" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS643" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT643" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU643" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV643" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B644" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P644" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S644" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T644" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U644" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V644" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W644" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X644" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB644" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC644" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD644" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI644" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ644" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK644" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL644" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM644" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN644" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO644" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP644" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ644" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR644" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS644" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT644" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU644" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV644" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B645" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P645" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S645" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T645" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U645" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V645" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W645" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X645" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB645" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC645" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD645" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI645" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ645" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK645" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL645" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM645" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN645" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO645" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP645" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ645" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR645" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS645" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT645" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU645" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV645" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B646" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P646" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S646" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T646" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U646" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V646" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W646" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X646" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB646" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC646" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD646" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI646" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ646" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK646" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL646" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM646" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN646" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO646" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP646" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ646" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR646" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS646" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT646" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU646" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV646" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B647" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P647" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S647" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T647" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U647" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V647" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W647" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X647" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB647" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC647" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD647" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI647" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ647" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK647" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL647" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM647" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN647" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO647" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP647" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ647" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR647" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS647" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT647" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU647" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV647" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B648" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P648" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S648" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T648" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U648" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V648" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W648" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X648" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB648" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC648" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD648" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI648" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ648" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK648" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL648" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM648" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN648" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO648" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP648" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ648" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR648" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS648" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT648" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU648" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV648" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B649" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P649" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S649" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T649" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U649" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V649" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W649" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X649" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB649" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC649" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD649" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI649" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ649" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK649" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL649" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM649" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN649" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO649" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP649" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ649" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR649" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS649" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT649" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU649" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV649" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/admin_testy/reporty_google_testy/google_data/Pobočky/Předloha/Databaze Zličín 2024.xlsx
+++ b/admin_testy/reporty_google_testy/google_data/Pobočky/Předloha/Databaze Zličín 2024.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2184" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2208" uniqueCount="66">
   <si>
     <t>Datum</t>
   </si>
@@ -48634,6 +48634,646 @@
         <v>0.09523809523809523</v>
       </c>
     </row>
+    <row r="650">
+      <c r="A650" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B650" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P650" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S650" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T650" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U650" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V650" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W650" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X650" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB650" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC650" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD650" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI650" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ650" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK650" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL650" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM650" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN650" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO650" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP650" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ650" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR650" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS650" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT650" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU650" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV650" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B651" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P651" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S651" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T651" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U651" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V651" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W651" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X651" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB651" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC651" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD651" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI651" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ651" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK651" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL651" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM651" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN651" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO651" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP651" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ651" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR651" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS651" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT651" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU651" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV651" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B652" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P652" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S652" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T652" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U652" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V652" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W652" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X652" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB652" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC652" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD652" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI652" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ652" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK652" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL652" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM652" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN652" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO652" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP652" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ652" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR652" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS652" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT652" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU652" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV652" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B653" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P653" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S653" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T653" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U653" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V653" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W653" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X653" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB653" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC653" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD653" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI653" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ653" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK653" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL653" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM653" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN653" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO653" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP653" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ653" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR653" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS653" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT653" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU653" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV653" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B654" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P654" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S654" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T654" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U654" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V654" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W654" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X654" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB654" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC654" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD654" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI654" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ654" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK654" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL654" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM654" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN654" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO654" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP654" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ654" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR654" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS654" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT654" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU654" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV654" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B655" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P655" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S655" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T655" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U655" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V655" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W655" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X655" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB655" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC655" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD655" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI655" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ655" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK655" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL655" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM655" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN655" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO655" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP655" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ655" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR655" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS655" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT655" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU655" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV655" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B656" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P656" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S656" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T656" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U656" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V656" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W656" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X656" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB656" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC656" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD656" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI656" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ656" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK656" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL656" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM656" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN656" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO656" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP656" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ656" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR656" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS656" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT656" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU656" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV656" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B657" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P657" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S657" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T657" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U657" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V657" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W657" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X657" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB657" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC657" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD657" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI657" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ657" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK657" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL657" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM657" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN657" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO657" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP657" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ657" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR657" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS657" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT657" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU657" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV657" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/admin_testy/reporty_google_testy/google_data/Pobočky/Předloha/Databaze Zličín 2024.xlsx
+++ b/admin_testy/reporty_google_testy/google_data/Pobočky/Předloha/Databaze Zličín 2024.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2208" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2214" uniqueCount="66">
   <si>
     <t>Datum</t>
   </si>
@@ -49274,6 +49274,166 @@
         <v>0.09523809523809523</v>
       </c>
     </row>
+    <row r="658">
+      <c r="A658" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B658" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P658" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S658" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T658" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U658" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V658" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W658" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X658" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB658" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC658" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD658" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI658" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ658" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK658" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL658" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM658" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN658" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO658" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP658" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ658" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR658" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS658" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT658" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU658" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV658" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B659" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P659" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S659" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T659" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U659" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V659" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W659" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X659" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB659" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC659" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD659" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI659" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ659" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK659" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL659" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM659" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN659" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO659" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP659" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ659" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR659" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS659" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT659" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU659" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV659" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/admin_testy/reporty_google_testy/google_data/Pobočky/Předloha/Databaze Zličín 2024.xlsx
+++ b/admin_testy/reporty_google_testy/google_data/Pobočky/Předloha/Databaze Zličín 2024.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2214" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2241" uniqueCount="66">
   <si>
     <t>Datum</t>
   </si>
@@ -49434,6 +49434,726 @@
         <v>0.09523809523809523</v>
       </c>
     </row>
+    <row r="660">
+      <c r="A660" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B660" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P660" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S660" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T660" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U660" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V660" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W660" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X660" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB660" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC660" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD660" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI660" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ660" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK660" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL660" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM660" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN660" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO660" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP660" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ660" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR660" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS660" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT660" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU660" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV660" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B661" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P661" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S661" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T661" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U661" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V661" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W661" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X661" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB661" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC661" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD661" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI661" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ661" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK661" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL661" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM661" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN661" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO661" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP661" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ661" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR661" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS661" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT661" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU661" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV661" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B662" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P662" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S662" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T662" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U662" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V662" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W662" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X662" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB662" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC662" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD662" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI662" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ662" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK662" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL662" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM662" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN662" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO662" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP662" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ662" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR662" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS662" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT662" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU662" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV662" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B663" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P663" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S663" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T663" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U663" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V663" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W663" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X663" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB663" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC663" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD663" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI663" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ663" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK663" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL663" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM663" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN663" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO663" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP663" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ663" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR663" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS663" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT663" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU663" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV663" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B664" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P664" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S664" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T664" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U664" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V664" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W664" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X664" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB664" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC664" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD664" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI664" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ664" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK664" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL664" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM664" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN664" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO664" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP664" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ664" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR664" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS664" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT664" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU664" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV664" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B665" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P665" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S665" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T665" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U665" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V665" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W665" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X665" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB665" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC665" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD665" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI665" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ665" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK665" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL665" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM665" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN665" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO665" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP665" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ665" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR665" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS665" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT665" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU665" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV665" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B666" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P666" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S666" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T666" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U666" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V666" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W666" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X666" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB666" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC666" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD666" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI666" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ666" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK666" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL666" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM666" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN666" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO666" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP666" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ666" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR666" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS666" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT666" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU666" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV666" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B667" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P667" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S667" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T667" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U667" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V667" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W667" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X667" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB667" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC667" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD667" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI667" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ667" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK667" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL667" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM667" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN667" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO667" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP667" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ667" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR667" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS667" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT667" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU667" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV667" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B668" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P668" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S668" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T668" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U668" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V668" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W668" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X668" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB668" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC668" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD668" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI668" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ668" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK668" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL668" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM668" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN668" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO668" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP668" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ668" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR668" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS668" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT668" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU668" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV668" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/admin_testy/reporty_google_testy/google_data/Pobočky/Předloha/Databaze Zličín 2024.xlsx
+++ b/admin_testy/reporty_google_testy/google_data/Pobočky/Předloha/Databaze Zličín 2024.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2241" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2250" uniqueCount="66">
   <si>
     <t>Datum</t>
   </si>
@@ -50154,6 +50154,246 @@
         <v>0.09523809523809523</v>
       </c>
     </row>
+    <row r="669">
+      <c r="A669" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B669" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P669" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S669" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T669" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U669" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V669" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W669" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X669" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB669" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC669" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD669" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI669" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ669" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK669" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL669" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM669" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN669" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO669" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP669" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ669" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR669" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS669" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT669" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU669" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV669" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B670" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P670" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S670" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T670" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U670" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V670" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W670" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X670" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB670" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC670" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD670" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI670" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ670" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK670" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL670" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM670" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN670" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO670" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP670" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ670" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR670" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS670" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT670" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU670" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV670" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B671" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P671" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="S671" s="3">
+        <v>14166.0</v>
+      </c>
+      <c r="T671" s="3">
+        <v>2963.0</v>
+      </c>
+      <c r="U671" s="3">
+        <v>6584.0</v>
+      </c>
+      <c r="V671" s="3">
+        <v>8838.0</v>
+      </c>
+      <c r="W671" s="3">
+        <v>795.0</v>
+      </c>
+      <c r="X671" s="3">
+        <v>3398.0</v>
+      </c>
+      <c r="AB671" s="3">
+        <v>42501.5</v>
+      </c>
+      <c r="AC671" s="3">
+        <v>-9155.5</v>
+      </c>
+      <c r="AD671" s="3">
+        <v>0.01004011623119184</v>
+      </c>
+      <c r="AI671" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AJ671" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK671" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL671" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="AM671" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN671" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AO671" s="3">
+        <v>100.0</v>
+      </c>
+      <c r="AP671" s="3">
+        <v>21.0</v>
+      </c>
+      <c r="AQ671" s="3">
+        <v>165.0</v>
+      </c>
+      <c r="AR671" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AS671" s="3">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AT671" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AU671" s="3">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AV671" s="3">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
